--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 04/09/2026, 14:13</x:t>
+    <x:t>Conta: 18466421 | 10/09/2026, 14:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 10/09/2026, 14:04</x:t>
+    <x:t>Conta: 18466421 | 21/09/2026, 16:44</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 21/09/2026, 16:44</x:t>
+    <x:t>Conta: 18466421 | 23/09/2026, 09:35</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 18466421.xlsx
+++ b/data/positions/Posição Consolidada - 18466421.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 18466421 | 23/09/2026, 09:35</x:t>
+    <x:t>Conta: 18466421 | 27/10/2026, 19:03</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,7 +34,10 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 0,00</x:t>
+    <x:t>100%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 46,89</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
@@ -65,6 +68,9 @@
   </x:si>
   <x:si>
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46,89</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -668,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>0</x:v>
+        <x:v>46.89</x:v>
       </x:c>
       <x:c r="B4" s="7">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>0</x:v>
+        <x:v>46.89</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -715,7 +721,7 @@
     </x:row>
     <x:row r="7" spans="1:11" ht="45" customHeight="1">
       <x:c r="A7" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9"/>
       <x:c r="C7" s="9"/>
@@ -727,7 +733,7 @@
       <x:c r="I7" s="9"/>
       <x:c r="J7" s="9"/>
       <x:c r="K7" s="10" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -748,69 +754,69 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K9" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
